--- a/Отчёты/098_Отчёт.xlsx
+++ b/Отчёты/098_Отчёт.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,11 +26,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00000000"/>
+      <sz val="12"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -39,8 +44,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004F81BD"/>
-        <bgColor rgb="004F81BD"/>
+        <fgColor rgb="00F5F5DC"/>
+        <bgColor rgb="00F5F5DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ADD8E6"/>
+        <bgColor rgb="00ADD8E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -64,10 +75,12 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,26 +449,26 @@
   <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Parameter</t>
+          <t>Параметр</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Значение</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Папка</t>
+          <t>Имя папки</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -467,31 +480,31 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>aRa (intercept)</t>
+          <t>a (Alfa)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>536.045</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>bRa (slope)</t>
+          <t>b (Alfa)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9.866</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>P(2700)</t>
+          <t>НУД α, № канала (2700)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -503,7 +516,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>P(4385.6)</t>
+          <t>ВУД ROI 3, № канала (4385.6)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -515,7 +528,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>P(5687.5)</t>
+          <t>НУД ROI 2, № канала (5687.5)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -527,7 +540,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>P(6192.35)</t>
+          <t>НУД ROI 6, № канала (6192.35)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -539,7 +552,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>P(6337.7)</t>
+          <t>НУД ROI 4, № канала (6337.7)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -551,7 +564,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>P(8044.6)</t>
+          <t>НУД ROI 5, № канала (8044.6)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -563,7 +576,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ra</t>
+          <t>K(Po218)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -587,7 +600,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Пик Am241: x</t>
+          <t>Пик Am241</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -599,24 +612,24 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>NUD_b</t>
+          <t>НУД β</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>VUD_b</t>
+          <t>ВУД β</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>200.000</t>
         </is>
       </c>
     </row>
@@ -635,24 +648,24 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>intercept (Beta)</t>
+          <t>a (Beta)</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-71.957</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>slope (Beta)</t>
+          <t>b (Beta)</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>10.878</t>
         </is>
       </c>
     </row>

--- a/Отчёты/098_Отчёт.xlsx
+++ b/Отчёты/098_Отчёт.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>Отсутствует</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>Отсутствует</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>Отсутствует</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>Отсутствует</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>Отсутствует</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>Отсутствует</t>
         </is>
       </c>
     </row>
